--- a/data/trans_orig/P32D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32D_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año en 2023</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36434</t>
+          <t>37162</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22964</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43847</t>
+          <t>42907</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203764</t>
+          <t>203036</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220878</t>
+          <t>221566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56386</t>
+          <t>56453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63813</t>
+          <t>63885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>262344</t>
+          <t>263284</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>283227</t>
+          <t>282543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72924</t>
+          <t>72682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114085</t>
+          <t>115345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35974</t>
+          <t>38662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72893</t>
+          <t>74557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143673</t>
+          <t>142975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>868494</t>
+          <t>867234</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>909655</t>
+          <t>909897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>672738</t>
+          <t>670050</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>700058</t>
+          <t>699887</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1547617</t>
+          <t>1548315</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1618397</t>
+          <t>1616733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>16713</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35555</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17403</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37820</t>
+          <t>38869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>38144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67752</t>
+          <t>66846</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306445</t>
+          <t>306008</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325599</t>
+          <t>325287</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>207138</t>
+          <t>206089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>227555</t>
+          <t>227808</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>519206</t>
+          <t>520112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>548569</t>
+          <t>548814</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121201</t>
+          <t>119882</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172826</t>
+          <t>168844</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25872</t>
+          <t>26976</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76327</t>
+          <t>74364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149218</t>
+          <t>149642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>232982</t>
+          <t>235327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1391951</t>
+          <t>1395933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1443576</t>
+          <t>1444895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>943336</t>
+          <t>945299</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>993791</t>
+          <t>992687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2351458</t>
+          <t>2349113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2435222</t>
+          <t>2434798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32D_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18632</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37162</t>
+          <t>42115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32065</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>25030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42907</t>
+          <t>47033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>213109</t>
+          <t>225397</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203036</t>
+          <t>212446</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>221566</t>
+          <t>233632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61017</t>
+          <t>67720</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56453</t>
+          <t>61037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63885</t>
+          <t>70718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>274126</t>
+          <t>293118</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>263284</t>
+          <t>281078</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>282543</t>
+          <t>303081</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>240198</t>
+          <t>254561</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>240198</t>
+          <t>254561</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>240198</t>
+          <t>254561</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65993</t>
+          <t>73549</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65993</t>
+          <t>73549</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65993</t>
+          <t>73549</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>306191</t>
+          <t>328111</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>306191</t>
+          <t>328111</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>306191</t>
+          <t>328111</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91591</t>
+          <t>104541</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72682</t>
+          <t>82013</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115345</t>
+          <t>130964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>30058</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>20970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38662</t>
+          <t>43266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>114540</t>
+          <t>134599</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74557</t>
+          <t>110873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142975</t>
+          <t>162380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>890988</t>
+          <t>939891</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>867234</t>
+          <t>913468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>909897</t>
+          <t>962419</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>685763</t>
+          <t>529279</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>670050</t>
+          <t>516071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>699887</t>
+          <t>538367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1576750</t>
+          <t>1469170</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1548315</t>
+          <t>1441389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1616733</t>
+          <t>1492896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>982579</t>
+          <t>1044432</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>982579</t>
+          <t>1044432</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>982579</t>
+          <t>1044432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>708712</t>
+          <t>559337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>708712</t>
+          <t>559337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>708712</t>
+          <t>559337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1691290</t>
+          <t>1603769</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1691290</t>
+          <t>1603769</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1691290</t>
+          <t>1603769</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>37927</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>27576</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>18313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38869</t>
+          <t>41526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>51423</t>
+          <t>54495</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38144</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66846</t>
+          <t>71865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>316731</t>
+          <t>338451</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306008</t>
+          <t>327443</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325287</t>
+          <t>347458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218804</t>
+          <t>241051</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206089</t>
+          <t>227101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>227808</t>
+          <t>250314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>535535</t>
+          <t>579502</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>520112</t>
+          <t>562132</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>548814</t>
+          <t>593441</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>342000</t>
+          <t>365370</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>342000</t>
+          <t>365370</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>342000</t>
+          <t>365370</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>244958</t>
+          <t>268627</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>244958</t>
+          <t>268627</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>244958</t>
+          <t>268627</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>586958</t>
+          <t>633997</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>586958</t>
+          <t>633997</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>586958</t>
+          <t>633997</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>143949</t>
+          <t>160624</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>119882</t>
+          <t>133499</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168844</t>
+          <t>189379</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54079</t>
+          <t>63463</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26976</t>
+          <t>49325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74364</t>
+          <t>81220</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>198028</t>
+          <t>224087</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149642</t>
+          <t>196806</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235327</t>
+          <t>261321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1420828</t>
+          <t>1503739</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1395933</t>
+          <t>1474984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1444895</t>
+          <t>1530864</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>965584</t>
+          <t>838050</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>945299</t>
+          <t>820293</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>992687</t>
+          <t>852188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2386412</t>
+          <t>2341790</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2349113</t>
+          <t>2304556</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2434798</t>
+          <t>2369071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1564777</t>
+          <t>1664363</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1564777</t>
+          <t>1664363</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1564777</t>
+          <t>1664363</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1019663</t>
+          <t>901513</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1019663</t>
+          <t>901513</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1019663</t>
+          <t>901513</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2584440</t>
+          <t>2565877</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2584440</t>
+          <t>2565877</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2584440</t>
+          <t>2565877</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
